--- a/data/trans_orig/P74A-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P74A-Estudios-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la situación laboral de su pareja en 2007</t>
+          <t>Población según la situación laboral de su pareja en 2007 (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>934</t>
+          <t>936</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8350</t>
+          <t>9267</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2078</t>
+          <t>2196</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14133</t>
+          <t>15131</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4565</t>
+          <t>4673</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>17491</t>
+          <t>18172</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,16%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2969</t>
+          <t>3469</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13671</t>
+          <t>13151</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,82 +860,82 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
+          <t>1,78%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>12100</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>6820</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>21759</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>1,47%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>0,83%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>2,65%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>19232</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>11546</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>28837</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>1,23%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>0,74%</t>
+        </is>
+      </c>
+      <c r="W5" s="2" t="inlineStr">
+        <is>
           <t>1,85%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>12100</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>6587</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>21008</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>1,47%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>0,8%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>2,56%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>19232</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>12162</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>29008</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>1,23%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>0,78%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>1,86%</t>
         </is>
       </c>
     </row>
@@ -963,7 +963,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6197</t>
+          <t>6538</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,62 +993,62 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>1962</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>1936</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>6429</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>0,13%</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>0,24%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>1962</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>6666</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>0,13%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,41%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>497076</t>
+          <t>495349</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>546719</t>
+          <t>543959</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>67,27%</t>
+          <t>67,04%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>73,99%</t>
+          <t>73,62%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10396</t>
+          <t>10882</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>489116</t>
+          <t>484593</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>559892</t>
+          <t>560741</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>31,34%</t>
+          <t>31,05%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>35,87%</t>
+          <t>35,93%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>52112</t>
+          <t>52505</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>82554</t>
+          <t>82532</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>385100</t>
+          <t>386122</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>443062</t>
+          <t>444323</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>46,86%</t>
+          <t>46,99%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>53,91%</t>
+          <t>54,07%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>444523</t>
+          <t>446771</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>518966</t>
+          <t>517850</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>28,48%</t>
+          <t>28,63%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>33,25%</t>
+          <t>33,18%</t>
         </is>
       </c>
     </row>
@@ -1297,97 +1297,97 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>1060</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>1889</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>5849</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>0,13%</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>0,26%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>0,71%</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="R9" s="2" t="inlineStr">
         <is>
           <t>1060</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr">
+      <c r="S9" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>5334</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>0,13%</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>6179</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>0,07%</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>0,65%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>1060</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>5309</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>0,07%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,4%</t>
         </is>
       </c>
     </row>
@@ -1410,12 +1410,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7532</t>
+          <t>7983</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21984</t>
+          <t>21785</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1425,12 +1425,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1445,12 +1445,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14871</t>
+          <t>14082</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>33290</t>
+          <t>33065</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1460,12 +1460,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1480,12 +1480,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>26259</t>
+          <t>26517</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>48369</t>
+          <t>50046</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1495,12 +1495,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,21%</t>
         </is>
       </c>
     </row>
@@ -1523,12 +1523,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>105608</t>
+          <t>105653</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>147910</t>
+          <t>147257</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1538,12 +1538,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1558,12 +1558,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>334718</t>
+          <t>332967</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>392489</t>
+          <t>390295</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1573,12 +1573,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>40,73%</t>
+          <t>40,52%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>47,76%</t>
+          <t>47,49%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1593,12 +1593,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>454985</t>
+          <t>451957</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>525898</t>
+          <t>529095</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1608,12 +1608,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>29,15%</t>
+          <t>28,96%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>33,7%</t>
+          <t>33,9%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>968</t>
+          <t>975</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11495</t>
+          <t>12254</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2482</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12153</t>
+          <t>12458</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4906</t>
+          <t>4510</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>18108</t>
+          <t>17746</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,87%</t>
         </is>
       </c>
     </row>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>9352</t>
+          <t>7270</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3194</t>
+          <t>3071</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>13600</t>
+          <t>15101</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4011</t>
+          <t>4032</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>16844</t>
+          <t>16253</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,8%</t>
         </is>
       </c>
     </row>
@@ -1979,12 +1979,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4368</t>
+          <t>3965</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>20339</t>
+          <t>19957</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1994,12 +1994,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2014,12 +2014,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1985</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2029,12 +2029,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2049,12 +2049,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>3585</t>
+          <t>3861</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>18775</t>
+          <t>19932</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2064,12 +2064,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,98%</t>
         </is>
       </c>
     </row>
@@ -2092,12 +2092,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>541096</t>
+          <t>539100</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>606747</t>
+          <t>602702</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2107,12 +2107,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>52,15%</t>
+          <t>51,96%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>58,48%</t>
+          <t>58,09%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6596</t>
+          <t>6561</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,7 +2147,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2162,12 +2162,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>534167</t>
+          <t>528392</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>618214</t>
+          <t>614715</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2177,12 +2177,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>30,3%</t>
+          <t>30,13%</t>
         </is>
       </c>
     </row>
@@ -2205,12 +2205,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7210</t>
+          <t>7151</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>23568</t>
+          <t>23775</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2240,12 +2240,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>70641</t>
+          <t>70701</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>106785</t>
+          <t>107755</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2255,12 +2255,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2275,12 +2275,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>83104</t>
+          <t>83136</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>122996</t>
+          <t>123918</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,7 +2295,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,07%</t>
         </is>
       </c>
     </row>
@@ -2323,7 +2323,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>9146</t>
+          <t>9151</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2353,62 +2353,62 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>1826</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>1985</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
+      <c r="T18" s="2" t="inlineStr">
+        <is>
+          <t>9163</t>
+        </is>
+      </c>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>0,09%</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>0,2%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>1826</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>14565</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>0,09%</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,45%</t>
         </is>
       </c>
     </row>
@@ -2431,12 +2431,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>45224</t>
+          <t>45116</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>75329</t>
+          <t>75378</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2446,12 +2446,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2466,12 +2466,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>27327</t>
+          <t>27757</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>52701</t>
+          <t>52202</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2481,12 +2481,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2501,12 +2501,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>78919</t>
+          <t>80542</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>116794</t>
+          <t>119105</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2516,12 +2516,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,84%</t>
         </is>
       </c>
     </row>
@@ -2544,12 +2544,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>345496</t>
+          <t>344015</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>406744</t>
+          <t>406721</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>33,16%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>39,21%</t>
+          <t>39,2%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2579,12 +2579,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>838292</t>
+          <t>840910</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>883082</t>
+          <t>883494</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2594,12 +2594,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>83,6%</t>
+          <t>83,86%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>88,07%</t>
+          <t>88,11%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2614,12 +2614,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1192906</t>
+          <t>1191797</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1286506</t>
+          <t>1280603</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2629,12 +2629,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>58,47%</t>
+          <t>58,42%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>63,06%</t>
+          <t>62,77%</t>
         </is>
       </c>
     </row>
@@ -2779,7 +2779,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6231</t>
+          <t>7156</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,7 +2794,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2809,62 +2809,62 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>1871</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>2050</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>6623</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>0,29%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>0,71%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>1871</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>6406</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,02%</t>
         </is>
       </c>
     </row>
@@ -2887,97 +2887,97 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>976</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>4887</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>0,34%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>0,55%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>1,7%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K23" s="2" t="inlineStr">
+      <c r="R23" s="2" t="inlineStr">
         <is>
           <t>976</t>
         </is>
       </c>
-      <c r="L23" s="2" t="inlineStr">
+      <c r="S23" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>5414</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>0,34%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>5458</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>0,15%</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>1,88%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>976</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>4897</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>0,15%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,84%</t>
         </is>
       </c>
     </row>
@@ -3000,12 +3000,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>937</t>
+          <t>1771</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>12628</t>
+          <t>11705</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3015,12 +3015,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3035,12 +3035,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2050</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3050,12 +3050,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3070,12 +3070,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>922</t>
+          <t>1026</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>11976</t>
+          <t>11801</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3085,12 +3085,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,81%</t>
         </is>
       </c>
     </row>
@@ -3113,12 +3113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>111199</t>
+          <t>109650</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>147440</t>
+          <t>146318</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3128,12 +3128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>30,6%</t>
+          <t>30,17%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>40,57%</t>
+          <t>40,26%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3148,12 +3148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2050</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3163,12 +3163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3183,12 +3183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>107412</t>
+          <t>106109</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>149530</t>
+          <t>149245</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3198,12 +3198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>22,93%</t>
         </is>
       </c>
     </row>
@@ -3226,12 +3226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>7035</t>
+          <t>6862</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>24102</t>
+          <t>24273</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3241,12 +3241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3261,12 +3261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>8576</t>
+          <t>8030</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>24089</t>
+          <t>23953</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3276,12 +3276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3296,12 +3296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>18779</t>
+          <t>19029</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>42222</t>
+          <t>42447</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3311,12 +3311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,52%</t>
         </is>
       </c>
     </row>
@@ -3339,97 +3339,97 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>0,55%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K27" s="2" t="inlineStr">
+      <c r="R27" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>2050</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr">
+      <c r="S27" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T27" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U27" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O27" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P27" s="2" t="inlineStr">
-        <is>
-          <t>0,71%</t>
-        </is>
-      </c>
-      <c r="Q27" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R27" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S27" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T27" s="2" t="inlineStr">
-        <is>
-          <t>2035</t>
-        </is>
-      </c>
-      <c r="U27" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3452,12 +3452,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3599</t>
+          <t>3586</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>16973</t>
+          <t>16622</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3472,7 +3472,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3487,12 +3487,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>969</t>
+          <t>967</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>7438</t>
+          <t>8763</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3507,7 +3507,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3522,12 +3522,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>6016</t>
+          <t>6335</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>21203</t>
+          <t>21436</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,29%</t>
         </is>
       </c>
     </row>
@@ -3565,12 +3565,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>187447</t>
+          <t>187502</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>225202</t>
+          <t>227778</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3580,12 +3580,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>51,58%</t>
+          <t>51,59%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>61,96%</t>
+          <t>62,67%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3600,12 +3600,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>259322</t>
+          <t>258426</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>275327</t>
+          <t>275829</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3615,12 +3615,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>90,25%</t>
+          <t>89,93%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,99%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3635,12 +3635,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>450965</t>
+          <t>450724</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>498820</t>
+          <t>498096</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3650,12 +3650,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>69,29%</t>
+          <t>69,26%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>76,65%</t>
+          <t>76,54%</t>
         </is>
       </c>
     </row>
@@ -3795,12 +3795,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>3933</t>
+          <t>4509</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>17849</t>
+          <t>17646</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3810,12 +3810,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3830,12 +3830,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>6342</t>
+          <t>6286</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>21730</t>
+          <t>20973</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3850,7 +3850,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3865,12 +3865,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>13066</t>
+          <t>12696</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>33521</t>
+          <t>33030</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3880,12 +3880,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,78%</t>
         </is>
       </c>
     </row>
@@ -3908,12 +3908,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>3974</t>
+          <t>4294</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>15546</t>
+          <t>15994</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3923,12 +3923,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3943,12 +3943,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>12793</t>
+          <t>12616</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>30842</t>
+          <t>29959</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3958,12 +3958,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3978,12 +3978,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>20329</t>
+          <t>19615</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>40939</t>
+          <t>40989</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4021,12 +4021,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>8985</t>
+          <t>8866</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>27672</t>
+          <t>29207</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4036,12 +4036,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4056,12 +4056,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>1977</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>9325</t>
+          <t>8865</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>29331</t>
+          <t>27600</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,65%</t>
         </is>
       </c>
     </row>
@@ -4134,12 +4134,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>1174039</t>
+          <t>1173978</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>1265934</t>
+          <t>1267977</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4149,12 +4149,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>54,87%</t>
+          <t>54,86%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>59,16%</t>
+          <t>59,26%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4169,12 +4169,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>982</t>
+          <t>987</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>13408</t>
+          <t>12333</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4189,7 +4189,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>1167989</t>
+          <t>1165854</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>1288461</t>
+          <t>1288817</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>27,42%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>30,3%</t>
+          <t>30,31%</t>
         </is>
       </c>
     </row>
@@ -4247,12 +4247,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>74479</t>
+          <t>76496</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>112152</t>
+          <t>112681</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4262,12 +4262,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4282,12 +4282,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>477026</t>
+          <t>477575</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>555178</t>
+          <t>553038</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>22,61%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>26,19%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>564177</t>
+          <t>561459</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>655326</t>
+          <t>653263</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,36%</t>
         </is>
       </c>
     </row>
@@ -4365,7 +4365,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>10926</t>
+          <t>10276</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4380,7 +4380,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4400,7 +4400,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>5257</t>
+          <t>5838</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4415,7 +4415,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4435,7 +4435,7 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>11257</t>
+          <t>9094</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4450,7 +4450,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,21%</t>
         </is>
       </c>
     </row>
@@ -4473,12 +4473,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>63741</t>
+          <t>66440</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>99459</t>
+          <t>101891</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4488,12 +4488,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4508,12 +4508,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>48933</t>
+          <t>48793</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>79662</t>
+          <t>80321</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4523,12 +4523,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4543,12 +4543,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>122265</t>
+          <t>123011</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>171112</t>
+          <t>169233</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4558,12 +4558,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,98%</t>
         </is>
       </c>
     </row>
@@ -4586,12 +4586,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>665572</t>
+          <t>661222</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>754185</t>
+          <t>751568</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4601,12 +4601,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>31,1%</t>
+          <t>30,9%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>35,25%</t>
+          <t>35,12%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4621,12 +4621,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>1453645</t>
+          <t>1454674</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>1531984</t>
+          <t>1536015</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4636,12 +4636,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>68,83%</t>
+          <t>68,88%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>72,54%</t>
+          <t>72,73%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4656,12 +4656,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>2130627</t>
+          <t>2140430</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>2267754</t>
+          <t>2271614</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4671,12 +4671,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>50,11%</t>
+          <t>50,34%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>53,34%</t>
+          <t>53,43%</t>
         </is>
       </c>
     </row>
@@ -4852,7 +4852,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la situación laboral de su pareja en 2012</t>
+          <t>Población según la situación laboral de su pareja en 2012 (tasa de respuesta: 99,74%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5047,82 +5047,82 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>2075</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2058</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>7699</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,24%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>0,9%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>2075</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>7238</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,24%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>0,84%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>2075</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7324</t>
+          <t>7230</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5160,12 +5160,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3104</t>
+          <t>3092</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14711</t>
+          <t>13840</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5180,7 +5180,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5195,12 +5195,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>18600</t>
+          <t>18980</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>41153</t>
+          <t>41628</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5210,12 +5210,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5230,12 +5230,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>24812</t>
+          <t>25048</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>50097</t>
+          <t>48963</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5245,12 +5245,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,16%</t>
         </is>
       </c>
     </row>
@@ -5273,12 +5273,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>971</t>
+          <t>995</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9768</t>
+          <t>8943</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5293,7 +5293,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5313,7 +5313,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9769</t>
+          <t>11275</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5328,7 +5328,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5343,12 +5343,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2862</t>
+          <t>2807</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>13571</t>
+          <t>13499</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5363,7 +5363,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,87%</t>
         </is>
       </c>
     </row>
@@ -5386,12 +5386,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>363595</t>
+          <t>365863</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>415366</t>
+          <t>416731</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5401,12 +5401,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>52,58%</t>
+          <t>52,91%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>60,07%</t>
+          <t>60,27%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5426,7 +5426,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5498</t>
+          <t>5955</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5441,7 +5441,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5456,12 +5456,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>359648</t>
+          <t>355154</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>428740</t>
+          <t>428766</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5471,7 +5471,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>22,94%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -5499,12 +5499,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>70237</t>
+          <t>68032</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>107123</t>
+          <t>105952</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5514,12 +5514,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5534,12 +5534,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>391778</t>
+          <t>392262</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>450120</t>
+          <t>452781</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5549,12 +5549,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>45,72%</t>
+          <t>45,77%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>52,52%</t>
+          <t>52,84%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5569,12 +5569,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>470323</t>
+          <t>468909</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>543001</t>
+          <t>545652</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5584,12 +5584,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>30,37%</t>
+          <t>30,28%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>35,07%</t>
+          <t>35,24%</t>
         </is>
       </c>
     </row>
@@ -5617,7 +5617,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>6288</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5652,7 +5652,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7611</t>
+          <t>6693</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5667,7 +5667,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5682,12 +5682,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1042</t>
+          <t>1038</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>10437</t>
+          <t>10496</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5702,7 +5702,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,68%</t>
         </is>
       </c>
     </row>
@@ -5725,12 +5725,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>58635</t>
+          <t>57138</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>92937</t>
+          <t>92821</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5760,12 +5760,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>94573</t>
+          <t>93613</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>133526</t>
+          <t>134090</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5775,12 +5775,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5795,12 +5795,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>160372</t>
+          <t>157938</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>210797</t>
+          <t>212351</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5810,12 +5810,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,71%</t>
         </is>
       </c>
     </row>
@@ -5838,12 +5838,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>107648</t>
+          <t>105555</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>148629</t>
+          <t>146838</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5853,12 +5853,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>21,24%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5873,12 +5873,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>258975</t>
+          <t>256517</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>316245</t>
+          <t>315555</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5888,12 +5888,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>30,22%</t>
+          <t>29,93%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>36,9%</t>
+          <t>36,82%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5908,12 +5908,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>380460</t>
+          <t>379182</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>450968</t>
+          <t>449910</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5923,12 +5923,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>29,12%</t>
+          <t>29,06%</t>
         </is>
       </c>
     </row>
@@ -6068,12 +6068,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>950</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14661</t>
+          <t>12982</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6103,12 +6103,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2084</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6118,12 +6118,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6138,12 +6138,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>949</t>
+          <t>950</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>13152</t>
+          <t>13958</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6158,7 +6158,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,59%</t>
         </is>
       </c>
     </row>
@@ -6181,12 +6181,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2793</t>
+          <t>2835</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>15361</t>
+          <t>15697</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6216,12 +6216,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>16954</t>
+          <t>16627</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>40344</t>
+          <t>40256</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6231,12 +6231,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6251,12 +6251,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>22054</t>
+          <t>22504</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>48315</t>
+          <t>49477</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6266,12 +6266,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,1%</t>
         </is>
       </c>
     </row>
@@ -6294,12 +6294,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3689</t>
+          <t>3730</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>14757</t>
+          <t>15189</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6309,12 +6309,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -6329,12 +6329,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1913</t>
+          <t>1948</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>13551</t>
+          <t>13669</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6349,7 +6349,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -6364,12 +6364,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>6843</t>
+          <t>7583</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>22668</t>
+          <t>23222</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -6379,12 +6379,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,99%</t>
         </is>
       </c>
     </row>
@@ -6407,12 +6407,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>469716</t>
+          <t>468479</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>538955</t>
+          <t>541302</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6422,12 +6422,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>38,72%</t>
+          <t>38,61%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>44,42%</t>
+          <t>44,62%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6447,7 +6447,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10735</t>
+          <t>9806</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6462,7 +6462,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6477,12 +6477,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>469167</t>
+          <t>463393</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>551495</t>
+          <t>546120</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>19,71%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>23,23%</t>
         </is>
       </c>
     </row>
@@ -6520,12 +6520,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>16410</t>
+          <t>17066</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>38002</t>
+          <t>38891</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6535,12 +6535,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6555,12 +6555,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>81387</t>
+          <t>79761</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>118822</t>
+          <t>119310</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6570,12 +6570,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6590,12 +6590,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>103145</t>
+          <t>102963</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>149394</t>
+          <t>149930</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,38%</t>
         </is>
       </c>
     </row>
@@ -6633,12 +6633,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1869</t>
+          <t>1882</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>10516</t>
+          <t>11330</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6648,12 +6648,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6673,7 +6673,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>7062</t>
+          <t>5862</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6688,7 +6688,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6703,12 +6703,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2145</t>
+          <t>1923</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>12587</t>
+          <t>13085</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,56%</t>
         </is>
       </c>
     </row>
@@ -6746,12 +6746,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>157645</t>
+          <t>154836</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>207741</t>
+          <t>204274</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6781,12 +6781,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>161644</t>
+          <t>161716</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>212717</t>
+          <t>217450</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6816,12 +6816,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>334028</t>
+          <t>331072</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>408937</t>
+          <t>401462</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>17,08%</t>
         </is>
       </c>
     </row>
@@ -6859,12 +6859,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>445083</t>
+          <t>440415</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>514097</t>
+          <t>517676</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>36,69%</t>
+          <t>36,3%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>42,38%</t>
+          <t>42,67%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>784945</t>
+          <t>783331</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>848174</t>
+          <t>848231</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6909,7 +6909,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>69,02%</t>
+          <t>68,88%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -6929,12 +6929,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1247285</t>
+          <t>1251504</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1343739</t>
+          <t>1351555</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>53,07%</t>
+          <t>53,24%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>57,17%</t>
+          <t>57,5%</t>
         </is>
       </c>
     </row>
@@ -7094,7 +7094,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>11086</t>
+          <t>10543</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7109,7 +7109,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7129,7 +7129,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>9336</t>
+          <t>7668</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7144,7 +7144,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7164,7 +7164,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>12977</t>
+          <t>14832</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7179,7 +7179,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,46%</t>
         </is>
       </c>
     </row>
@@ -7207,7 +7207,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>6423</t>
+          <t>7535</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7222,7 +7222,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7237,12 +7237,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>936</t>
+          <t>933</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>11261</t>
+          <t>10037</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7257,7 +7257,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7272,12 +7272,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1962</t>
+          <t>2058</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>12295</t>
+          <t>12773</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -7287,12 +7287,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,12%</t>
         </is>
       </c>
     </row>
@@ -7315,12 +7315,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4309</t>
+          <t>4914</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>20275</t>
+          <t>20714</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -7355,7 +7355,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>5443</t>
+          <t>4889</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -7370,7 +7370,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -7385,12 +7385,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>5488</t>
+          <t>5523</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>21713</t>
+          <t>22118</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -7400,12 +7400,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,67%</t>
         </is>
       </c>
     </row>
@@ -7428,12 +7428,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>52868</t>
+          <t>52097</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>85231</t>
+          <t>84049</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>27,95%</t>
+          <t>27,56%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7463,12 +7463,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2161</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7478,12 +7478,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7498,12 +7498,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>53006</t>
+          <t>53567</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>85631</t>
+          <t>86051</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7513,12 +7513,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>14,29%</t>
         </is>
       </c>
     </row>
@@ -7541,12 +7541,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>4808</t>
+          <t>4473</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>22990</t>
+          <t>22434</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7556,12 +7556,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7576,12 +7576,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>11400</t>
+          <t>11618</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>32033</t>
+          <t>31307</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7591,12 +7591,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7611,12 +7611,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>19159</t>
+          <t>19703</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>46165</t>
+          <t>45748</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7626,12 +7626,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,6%</t>
         </is>
       </c>
     </row>
@@ -7654,97 +7654,97 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>2168</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>0,71%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K27" s="2" t="inlineStr">
+      <c r="R27" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>2161</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr">
+      <c r="S27" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T27" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U27" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O27" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P27" s="2" t="inlineStr">
-        <is>
-          <t>0,73%</t>
-        </is>
-      </c>
-      <c r="Q27" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R27" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S27" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T27" s="2" t="inlineStr">
-        <is>
-          <t>2169</t>
-        </is>
-      </c>
-      <c r="U27" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -7767,12 +7767,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>16653</t>
+          <t>18306</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>41645</t>
+          <t>42249</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7782,12 +7782,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7802,12 +7802,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>10314</t>
+          <t>10594</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>27650</t>
+          <t>27606</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7817,12 +7817,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7837,12 +7837,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>32796</t>
+          <t>32261</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>61503</t>
+          <t>62622</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7852,12 +7852,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,4%</t>
         </is>
       </c>
     </row>
@@ -7880,12 +7880,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>163398</t>
+          <t>163628</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>201366</t>
+          <t>201251</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7895,12 +7895,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>53,58%</t>
+          <t>53,66%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>66,03%</t>
+          <t>66,0%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7915,12 +7915,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>238858</t>
+          <t>238896</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>266018</t>
+          <t>264906</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7930,12 +7930,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>80,34%</t>
+          <t>80,35%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>89,47%</t>
+          <t>89,1%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7950,12 +7950,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>412113</t>
+          <t>412539</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>460357</t>
+          <t>459850</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7965,12 +7965,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>68,43%</t>
+          <t>68,5%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>76,44%</t>
+          <t>76,35%</t>
         </is>
       </c>
     </row>
@@ -8110,12 +8110,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1873</t>
+          <t>1863</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>16741</t>
+          <t>16093</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8130,7 +8130,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8150,7 +8150,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>11401</t>
+          <t>11827</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8165,7 +8165,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8180,12 +8180,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>4296</t>
+          <t>4630</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>22438</t>
+          <t>21657</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8200,7 +8200,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,48%</t>
         </is>
       </c>
     </row>
@@ -8223,12 +8223,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>9255</t>
+          <t>9214</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>28038</t>
+          <t>28327</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8243,7 +8243,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8258,12 +8258,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>42702</t>
+          <t>43438</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>76216</t>
+          <t>78345</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8273,12 +8273,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8293,12 +8293,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>59293</t>
+          <t>57950</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>96010</t>
+          <t>95783</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8308,7 +8308,7 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -8336,12 +8336,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>13292</t>
+          <t>13897</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>35358</t>
+          <t>34861</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -8351,12 +8351,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -8371,12 +8371,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>3971</t>
+          <t>4777</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>19325</t>
+          <t>19237</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -8386,7 +8386,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -8406,12 +8406,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>21223</t>
+          <t>21700</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>45991</t>
+          <t>45954</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8421,7 +8421,7 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
@@ -8449,12 +8449,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>915572</t>
+          <t>913245</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>1012615</t>
+          <t>1009093</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8464,12 +8464,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>41,44%</t>
+          <t>41,33%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>45,83%</t>
+          <t>45,67%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>1037</t>
+          <t>1039</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>12305</t>
+          <t>13158</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8504,7 +8504,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8519,12 +8519,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>910541</t>
+          <t>911321</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>1026980</t>
+          <t>1027111</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8534,7 +8534,7 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -8562,12 +8562,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>104125</t>
+          <t>102959</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>150343</t>
+          <t>152054</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -8577,12 +8577,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -8597,12 +8597,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>498624</t>
+          <t>495959</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>583578</t>
+          <t>581203</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -8612,12 +8612,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>21,64%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>25,47%</t>
+          <t>25,36%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -8632,12 +8632,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>613243</t>
+          <t>615540</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>714644</t>
+          <t>713349</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -8647,12 +8647,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>15,85%</t>
         </is>
       </c>
     </row>
@@ -8675,12 +8675,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>2932</t>
+          <t>2919</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>13469</t>
+          <t>13674</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -8695,7 +8695,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -8710,12 +8710,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>989</t>
+          <t>992</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>8944</t>
+          <t>8851</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -8745,12 +8745,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>5093</t>
+          <t>5281</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>18489</t>
+          <t>18290</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -8760,7 +8760,7 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -8788,12 +8788,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>251459</t>
+          <t>250963</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>312391</t>
+          <t>315748</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -8803,12 +8803,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -8823,12 +8823,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>285619</t>
+          <t>285507</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>355542</t>
+          <t>350339</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -8843,7 +8843,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -8858,12 +8858,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>550862</t>
+          <t>551229</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>644807</t>
+          <t>647082</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -8873,12 +8873,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,38%</t>
         </is>
       </c>
     </row>
@@ -8901,12 +8901,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>747999</t>
+          <t>743686</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>836270</t>
+          <t>832856</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -8916,12 +8916,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>33,85%</t>
+          <t>33,66%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>37,85%</t>
+          <t>37,69%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -8936,12 +8936,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>1301443</t>
+          <t>1301316</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>1406146</t>
+          <t>1402010</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -8956,7 +8956,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>61,36%</t>
+          <t>61,18%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -8971,12 +8971,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>2074274</t>
+          <t>2072822</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>2218131</t>
+          <t>2215621</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -8986,12 +8986,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>46,08%</t>
+          <t>46,05%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>49,28%</t>
+          <t>49,22%</t>
         </is>
       </c>
     </row>
@@ -9167,7 +9167,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la situación laboral de su pareja en 2016</t>
+          <t>Población según la situación laboral de su pareja en 2016 (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9367,7 +9367,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6369</t>
+          <t>6759</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9382,7 +9382,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9397,12 +9397,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>975</t>
+          <t>986</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9786</t>
+          <t>9224</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9417,7 +9417,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9432,12 +9432,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2031</t>
+          <t>2045</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11867</t>
+          <t>12263</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9447,12 +9447,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,11%</t>
         </is>
       </c>
     </row>
@@ -9475,12 +9475,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2140</t>
+          <t>2075</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12728</t>
+          <t>12558</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9490,12 +9490,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9510,12 +9510,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2198</t>
+          <t>2271</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12789</t>
+          <t>14364</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9525,12 +9525,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9545,12 +9545,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>6397</t>
+          <t>6428</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>22444</t>
+          <t>21148</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9565,7 +9565,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,91%</t>
         </is>
       </c>
     </row>
@@ -9593,7 +9593,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5720</t>
+          <t>5798</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9608,7 +9608,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9623,62 +9623,62 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>1016</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>2079</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>4862</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>0,09%</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>0,35%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>1016</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>4703</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>0,09%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,44%</t>
         </is>
       </c>
     </row>
@@ -9701,12 +9701,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>278642</t>
+          <t>278183</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>323717</t>
+          <t>324669</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -9716,12 +9716,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>55,23%</t>
+          <t>55,14%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>64,17%</t>
+          <t>64,36%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9741,7 +9741,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5413</t>
+          <t>6037</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9771,12 +9771,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>277509</t>
+          <t>271937</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>335289</t>
+          <t>331315</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9786,12 +9786,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>24,62%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>30,36%</t>
+          <t>30,0%</t>
         </is>
       </c>
     </row>
@@ -9814,12 +9814,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>37880</t>
+          <t>37385</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>64258</t>
+          <t>64592</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9829,12 +9829,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9849,12 +9849,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>333838</t>
+          <t>333445</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>383375</t>
+          <t>380989</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9864,12 +9864,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>55,65%</t>
+          <t>55,59%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>63,91%</t>
+          <t>63,51%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9884,12 +9884,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>372547</t>
+          <t>373819</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>435557</t>
+          <t>437125</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9899,12 +9899,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>33,73%</t>
+          <t>33,85%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>39,44%</t>
+          <t>39,58%</t>
         </is>
       </c>
     </row>
@@ -9932,7 +9932,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4450</t>
+          <t>5076</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9947,7 +9947,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -9967,7 +9967,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7014</t>
+          <t>7075</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9982,7 +9982,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -9997,12 +9997,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>890</t>
+          <t>889</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>8794</t>
+          <t>7693</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10017,7 +10017,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,7%</t>
         </is>
       </c>
     </row>
@@ -10040,12 +10040,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>60141</t>
+          <t>59123</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>93223</t>
+          <t>91510</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10055,12 +10055,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10075,12 +10075,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>74863</t>
+          <t>74883</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>110262</t>
+          <t>109429</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10095,7 +10095,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10110,12 +10110,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>144202</t>
+          <t>142768</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>192236</t>
+          <t>190050</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10125,12 +10125,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,21%</t>
         </is>
       </c>
     </row>
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>55492</t>
+          <t>54822</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>87035</t>
+          <t>86539</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10168,12 +10168,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10188,12 +10188,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>116988</t>
+          <t>120030</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>157854</t>
+          <t>160573</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10203,12 +10203,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>26,31%</t>
+          <t>26,77%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10223,12 +10223,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>182207</t>
+          <t>183265</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>236759</t>
+          <t>234416</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10238,12 +10238,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>21,23%</t>
         </is>
       </c>
     </row>
@@ -10388,7 +10388,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6725</t>
+          <t>6711</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10418,12 +10418,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1112</t>
+          <t>1117</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10124</t>
+          <t>10545</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10438,7 +10438,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10453,12 +10453,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2128</t>
+          <t>2184</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>13072</t>
+          <t>12651</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10473,7 +10473,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,51%</t>
         </is>
       </c>
     </row>
@@ -10496,12 +10496,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5083</t>
+          <t>5285</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>22696</t>
+          <t>22338</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10511,12 +10511,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10531,12 +10531,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>9060</t>
+          <t>9141</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>26540</t>
+          <t>23340</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10546,12 +10546,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10566,12 +10566,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>15816</t>
+          <t>17288</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>38791</t>
+          <t>38680</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10581,7 +10581,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -10609,12 +10609,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4920</t>
+          <t>4905</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>17175</t>
+          <t>16572</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10629,7 +10629,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -10644,12 +10644,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1902</t>
+          <t>1896</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>12899</t>
+          <t>12538</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10664,7 +10664,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -10679,12 +10679,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>9123</t>
+          <t>8669</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>24699</t>
+          <t>24238</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10694,12 +10694,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,97%</t>
         </is>
       </c>
     </row>
@@ -10722,12 +10722,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>549664</t>
+          <t>549282</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>619228</t>
+          <t>622682</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>42,54%</t>
+          <t>42,51%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>47,92%</t>
+          <t>48,19%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10762,7 +10762,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6436</t>
+          <t>8324</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10777,7 +10777,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10792,12 +10792,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>539760</t>
+          <t>546195</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>630458</t>
+          <t>631756</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10807,12 +10807,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>21,88%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>25,3%</t>
         </is>
       </c>
     </row>
@@ -10835,12 +10835,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>20393</t>
+          <t>19798</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>40925</t>
+          <t>39554</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10870,12 +10870,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>161121</t>
+          <t>161813</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>216433</t>
+          <t>211460</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10905,12 +10905,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>189944</t>
+          <t>188134</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>249293</t>
+          <t>245110</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10920,12 +10920,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>9,82%</t>
         </is>
       </c>
     </row>
@@ -10948,97 +10948,97 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>1912</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>2051</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>6836</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>0,16%</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>0,16%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>0,57%</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K18" s="2" t="inlineStr">
+      <c r="R18" s="2" t="inlineStr">
         <is>
           <t>1912</t>
         </is>
       </c>
-      <c r="L18" s="2" t="inlineStr">
+      <c r="S18" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>5912</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>0,16%</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
+      <c r="T18" s="2" t="inlineStr">
+        <is>
+          <t>6390</t>
+        </is>
+      </c>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>0,08%</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>0,49%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>1912</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>7022</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>0,08%</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,26%</t>
         </is>
       </c>
     </row>
@@ -11061,12 +11061,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>190346</t>
+          <t>191572</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>246372</t>
+          <t>244651</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11076,12 +11076,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11096,12 +11096,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>162758</t>
+          <t>161837</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>212623</t>
+          <t>212270</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11111,12 +11111,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11131,12 +11131,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>366688</t>
+          <t>367147</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>441947</t>
+          <t>441470</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11146,12 +11146,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>17,68%</t>
         </is>
       </c>
     </row>
@@ -11174,12 +11174,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>405895</t>
+          <t>401527</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>473128</t>
+          <t>471793</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11189,12 +11189,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>31,41%</t>
+          <t>31,07%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>36,62%</t>
+          <t>36,51%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11209,12 +11209,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>765530</t>
+          <t>770481</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>833590</t>
+          <t>832799</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>63,54%</t>
+          <t>63,95%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>69,19%</t>
+          <t>69,13%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11244,12 +11244,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1186164</t>
+          <t>1184485</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1289859</t>
+          <t>1286736</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11259,12 +11259,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>47,51%</t>
+          <t>47,44%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>51,66%</t>
+          <t>51,53%</t>
         </is>
       </c>
     </row>
@@ -11409,7 +11409,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>7521</t>
+          <t>9389</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11424,7 +11424,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11444,7 +11444,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>5876</t>
+          <t>6243</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11459,7 +11459,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11479,7 +11479,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>9198</t>
+          <t>10678</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11494,7 +11494,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,58%</t>
         </is>
       </c>
     </row>
@@ -11522,7 +11522,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>5409</t>
+          <t>5551</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11537,7 +11537,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11552,62 +11552,62 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>1026</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>5158</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>0,15%</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>0,62%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>1026</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>5118</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>0,15%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,77%</t>
         </is>
       </c>
     </row>
@@ -11630,12 +11630,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2152</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>12919</t>
+          <t>13501</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11645,12 +11645,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11665,12 +11665,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -11680,12 +11680,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2854</t>
+          <t>2756</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>13286</t>
+          <t>13118</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -11715,12 +11715,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,95%</t>
         </is>
       </c>
     </row>
@@ -11743,12 +11743,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>73530</t>
+          <t>72481</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>106734</t>
+          <t>106769</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -11758,12 +11758,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>30,82%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -11793,12 +11793,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -11813,12 +11813,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>73278</t>
+          <t>72763</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>109698</t>
+          <t>110961</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -11828,12 +11828,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,47%</t>
         </is>
       </c>
     </row>
@@ -11856,12 +11856,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>8112</t>
+          <t>7438</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>23063</t>
+          <t>24334</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11871,12 +11871,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11891,12 +11891,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>17271</t>
+          <t>17317</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>37501</t>
+          <t>38544</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11906,12 +11906,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11926,12 +11926,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>28319</t>
+          <t>28311</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>56235</t>
+          <t>55546</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -11946,7 +11946,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,24%</t>
         </is>
       </c>
     </row>
@@ -11974,7 +11974,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>6636</t>
+          <t>5900</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -11989,7 +11989,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -12004,62 +12004,62 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr">
+        <is>
+          <t>1907</t>
+        </is>
+      </c>
+      <c r="S27" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr">
+      <c r="T27" s="2" t="inlineStr">
+        <is>
+          <t>5938</t>
+        </is>
+      </c>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>0,28%</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O27" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P27" s="2" t="inlineStr">
-        <is>
-          <t>0,62%</t>
-        </is>
-      </c>
-      <c r="Q27" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R27" s="2" t="inlineStr">
-        <is>
-          <t>1907</t>
-        </is>
-      </c>
-      <c r="S27" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T27" s="2" t="inlineStr">
-        <is>
-          <t>6477</t>
-        </is>
-      </c>
-      <c r="U27" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
-      <c r="V27" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,88%</t>
         </is>
       </c>
     </row>
@@ -12082,12 +12082,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>30508</t>
+          <t>29328</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>56063</t>
+          <t>56339</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -12097,12 +12097,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -12117,12 +12117,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>21012</t>
+          <t>20176</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>42618</t>
+          <t>40745</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -12132,12 +12132,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -12152,12 +12152,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>57286</t>
+          <t>57540</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>90472</t>
+          <t>90366</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -12167,12 +12167,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,41%</t>
         </is>
       </c>
     </row>
@@ -12195,12 +12195,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>171967</t>
+          <t>171166</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>209628</t>
+          <t>210007</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -12210,12 +12210,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>49,65%</t>
+          <t>49,41%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>60,52%</t>
+          <t>60,63%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -12230,12 +12230,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>253608</t>
+          <t>255802</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>281895</t>
+          <t>283233</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -12245,12 +12245,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>77,45%</t>
+          <t>78,12%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>86,08%</t>
+          <t>86,49%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -12265,12 +12265,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>432615</t>
+          <t>433317</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>483991</t>
+          <t>484453</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -12280,12 +12280,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>64,2%</t>
+          <t>64,3%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>71,82%</t>
+          <t>71,89%</t>
         </is>
       </c>
     </row>
@@ -12425,12 +12425,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1851</t>
+          <t>1821</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>12043</t>
+          <t>13378</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -12440,12 +12440,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -12460,12 +12460,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>4014</t>
+          <t>4928</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>16832</t>
+          <t>17407</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -12475,12 +12475,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -12495,12 +12495,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>7877</t>
+          <t>8630</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>23427</t>
+          <t>24248</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -12510,12 +12510,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,57%</t>
         </is>
       </c>
     </row>
@@ -12538,12 +12538,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>10952</t>
+          <t>10413</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>30836</t>
+          <t>30533</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -12553,12 +12553,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -12573,12 +12573,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>13454</t>
+          <t>13388</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>32865</t>
+          <t>32794</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -12608,12 +12608,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>28442</t>
+          <t>28277</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>54008</t>
+          <t>56364</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -12623,12 +12623,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,32%</t>
         </is>
       </c>
     </row>
@@ -12651,12 +12651,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>9775</t>
+          <t>10481</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>26481</t>
+          <t>27266</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -12666,12 +12666,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -12686,12 +12686,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>1902</t>
+          <t>1891</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>11619</t>
+          <t>12959</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -12706,7 +12706,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -12721,12 +12721,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>13427</t>
+          <t>14119</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>32650</t>
+          <t>32826</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -12736,12 +12736,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,77%</t>
         </is>
       </c>
     </row>
@@ -12764,12 +12764,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>927757</t>
+          <t>927709</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>1024133</t>
+          <t>1022289</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -12784,7 +12784,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>47,79%</t>
+          <t>47,7%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -12799,12 +12799,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>1004</t>
+          <t>1008</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>9536</t>
+          <t>10545</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -12819,7 +12819,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -12834,12 +12834,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>925177</t>
+          <t>925674</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>1039927</t>
+          <t>1037282</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12849,12 +12849,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>21,65%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>24,26%</t>
         </is>
       </c>
     </row>
@@ -12877,12 +12877,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>75574</t>
+          <t>75904</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>112575</t>
+          <t>112850</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -12892,12 +12892,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -12912,12 +12912,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>527456</t>
+          <t>526275</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>613932</t>
+          <t>613606</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -12927,12 +12927,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>24,68%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>28,8%</t>
+          <t>28,78%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -12947,12 +12947,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>617397</t>
+          <t>616834</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>713978</t>
+          <t>712574</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -12962,12 +12962,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,67%</t>
         </is>
       </c>
     </row>
@@ -12990,12 +12990,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>885</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>7534</t>
+          <t>8326</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -13010,7 +13010,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -13025,12 +13025,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>1058</t>
+          <t>1008</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>9015</t>
+          <t>9434</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -13045,7 +13045,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -13060,12 +13060,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>2933</t>
+          <t>2812</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>12779</t>
+          <t>13255</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -13080,7 +13080,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,31%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>301791</t>
+          <t>302699</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>369563</t>
+          <t>374299</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>276685</t>
+          <t>277838</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>339195</t>
+          <t>341710</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>595785</t>
+          <t>593020</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>687829</t>
+          <t>690614</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>16,15%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>654497</t>
+          <t>651641</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>742097</t>
+          <t>743304</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>30,54%</t>
+          <t>30,41%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>34,63%</t>
+          <t>34,69%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>1164434</t>
+          <t>1164156</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>1256229</t>
+          <t>1255122</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>54,62%</t>
+          <t>54,6%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>58,92%</t>
+          <t>58,87%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1836864</t>
+          <t>1838484</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1966775</t>
+          <t>1974229</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>42,97%</t>
+          <t>43,0%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>46,01%</t>
+          <t>46,18%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P74A-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P74A-Estudios-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>936</t>
+          <t>931</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9267</t>
+          <t>9176</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2196</t>
+          <t>2084</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15131</t>
+          <t>13689</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4673</t>
+          <t>4690</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18172</t>
+          <t>17237</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,1%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3469</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13151</t>
+          <t>13344</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6820</t>
+          <t>6358</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21759</t>
+          <t>21321</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>11546</t>
+          <t>12325</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>28837</t>
+          <t>29905</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,92%</t>
         </is>
       </c>
     </row>
@@ -963,7 +963,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6538</t>
+          <t>6795</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>6429</t>
+          <t>6746</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,43%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>495349</t>
+          <t>497771</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>543959</t>
+          <t>546231</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>67,04%</t>
+          <t>67,37%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>73,62%</t>
+          <t>73,92%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10882</t>
+          <t>10401</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>484593</t>
+          <t>488102</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>560741</t>
+          <t>558952</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>31,05%</t>
+          <t>31,27%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>35,93%</t>
+          <t>35,81%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>52505</t>
+          <t>51349</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>82532</t>
+          <t>80017</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>386122</t>
+          <t>386336</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>444323</t>
+          <t>442784</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>46,99%</t>
+          <t>47,01%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>54,07%</t>
+          <t>53,88%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>446771</t>
+          <t>443910</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>517850</t>
+          <t>517899</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,7 +1269,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>28,63%</t>
+          <t>28,44%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5849</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,7 +1372,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>6179</t>
+          <t>5283</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,7 +1387,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,34%</t>
         </is>
       </c>
     </row>
@@ -1410,12 +1410,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7983</t>
+          <t>7899</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21785</t>
+          <t>23204</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1425,12 +1425,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1445,12 +1445,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14082</t>
+          <t>14187</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>33065</t>
+          <t>32702</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1460,12 +1460,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1480,12 +1480,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>26517</t>
+          <t>26224</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>50046</t>
+          <t>49628</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1495,12 +1495,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,18%</t>
         </is>
       </c>
     </row>
@@ -1523,12 +1523,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>105653</t>
+          <t>105802</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>147257</t>
+          <t>146867</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1538,12 +1538,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1558,12 +1558,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>332967</t>
+          <t>335997</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>390295</t>
+          <t>391415</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1573,12 +1573,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>40,52%</t>
+          <t>40,89%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>47,49%</t>
+          <t>47,63%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1593,12 +1593,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>451957</t>
+          <t>451157</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>529095</t>
+          <t>527580</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1608,12 +1608,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>28,96%</t>
+          <t>28,91%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>33,9%</t>
+          <t>33,8%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>975</t>
+          <t>972</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12254</t>
+          <t>11621</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2482</t>
+          <t>2052</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12458</t>
+          <t>12346</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4510</t>
+          <t>4628</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>17746</t>
+          <t>19204</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,94%</t>
         </is>
       </c>
     </row>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7270</t>
+          <t>8713</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3071</t>
+          <t>3079</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>15101</t>
+          <t>14769</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4032</t>
+          <t>3923</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>16253</t>
+          <t>15787</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,77%</t>
         </is>
       </c>
     </row>
@@ -1979,12 +1979,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3965</t>
+          <t>3670</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>19957</t>
+          <t>19078</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1994,12 +1994,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2049,12 +2049,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>3861</t>
+          <t>3848</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>19932</t>
+          <t>19595</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,96%</t>
         </is>
       </c>
     </row>
@@ -2092,12 +2092,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>539100</t>
+          <t>536899</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>602702</t>
+          <t>603897</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2107,12 +2107,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>51,96%</t>
+          <t>51,75%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>58,09%</t>
+          <t>58,21%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6561</t>
+          <t>6039</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,7 +2147,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2162,12 +2162,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>528392</t>
+          <t>532917</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>614715</t>
+          <t>614221</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2177,12 +2177,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>26,12%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>30,13%</t>
+          <t>30,11%</t>
         </is>
       </c>
     </row>
@@ -2205,12 +2205,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7151</t>
+          <t>7560</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>23775</t>
+          <t>23894</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2220,12 +2220,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2240,12 +2240,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>70701</t>
+          <t>70502</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>107755</t>
+          <t>107456</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2255,12 +2255,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2275,12 +2275,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>83136</t>
+          <t>82445</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>123918</t>
+          <t>124075</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2290,12 +2290,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,08%</t>
         </is>
       </c>
     </row>
@@ -2323,7 +2323,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>9151</t>
+          <t>10609</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,7 +2338,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2393,7 +2393,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>9163</t>
+          <t>9172</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2431,12 +2431,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>45116</t>
+          <t>45490</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>75378</t>
+          <t>76529</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2446,12 +2446,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2466,12 +2466,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>27757</t>
+          <t>27867</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>52202</t>
+          <t>52161</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2481,12 +2481,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2501,12 +2501,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>80542</t>
+          <t>80474</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>119105</t>
+          <t>118322</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2516,12 +2516,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,8%</t>
         </is>
       </c>
     </row>
@@ -2544,12 +2544,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>344015</t>
+          <t>344386</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>406721</t>
+          <t>411119</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>33,16%</t>
+          <t>33,19%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>39,2%</t>
+          <t>39,63%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2579,12 +2579,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>840910</t>
+          <t>836493</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>883494</t>
+          <t>881916</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2594,12 +2594,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>83,86%</t>
+          <t>83,42%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>88,11%</t>
+          <t>87,95%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2614,12 +2614,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1191797</t>
+          <t>1194028</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1280603</t>
+          <t>1281973</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2629,12 +2629,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>58,42%</t>
+          <t>58,52%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>62,77%</t>
+          <t>62,84%</t>
         </is>
       </c>
     </row>
@@ -2779,7 +2779,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>7156</t>
+          <t>5893</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,7 +2794,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2849,7 +2849,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6623</t>
+          <t>6465</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,7 +2864,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,99%</t>
         </is>
       </c>
     </row>
@@ -2927,7 +2927,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>4887</t>
+          <t>4932</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2942,7 +2942,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,7 +2962,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5458</t>
+          <t>4874</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2977,7 +2977,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,75%</t>
         </is>
       </c>
     </row>
@@ -3000,12 +3000,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1771</t>
+          <t>1775</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>11705</t>
+          <t>12625</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3070,12 +3070,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1026</t>
+          <t>929</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>11801</t>
+          <t>13361</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3085,12 +3085,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>2,05%</t>
         </is>
       </c>
     </row>
@@ -3113,12 +3113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>109650</t>
+          <t>110539</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>146318</t>
+          <t>147712</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3128,12 +3128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>30,41%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>40,26%</t>
+          <t>40,64%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3183,12 +3183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>106109</t>
+          <t>108340</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>149245</t>
+          <t>151350</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3198,12 +3198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>23,26%</t>
         </is>
       </c>
     </row>
@@ -3226,12 +3226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>6862</t>
+          <t>6830</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>24273</t>
+          <t>23460</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3241,12 +3241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3261,12 +3261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>8030</t>
+          <t>8759</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>23953</t>
+          <t>24900</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3276,12 +3276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3296,12 +3296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>19029</t>
+          <t>19064</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>42447</t>
+          <t>41411</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3311,12 +3311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,36%</t>
         </is>
       </c>
     </row>
@@ -3452,12 +3452,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3586</t>
+          <t>3707</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>16622</t>
+          <t>17675</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3467,12 +3467,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3487,12 +3487,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>967</t>
+          <t>966</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>8763</t>
+          <t>8384</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3507,7 +3507,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3522,12 +3522,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>6335</t>
+          <t>6167</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>21436</t>
+          <t>20749</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,19%</t>
         </is>
       </c>
     </row>
@@ -3565,12 +3565,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>187502</t>
+          <t>185955</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>227778</t>
+          <t>225811</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3580,12 +3580,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>51,59%</t>
+          <t>51,17%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>62,67%</t>
+          <t>62,13%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3600,12 +3600,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>258426</t>
+          <t>258053</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>275829</t>
+          <t>275468</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3615,12 +3615,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>89,93%</t>
+          <t>89,8%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3635,12 +3635,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>450724</t>
+          <t>451622</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>498096</t>
+          <t>497577</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3650,12 +3650,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>69,26%</t>
+          <t>69,4%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>76,54%</t>
+          <t>76,46%</t>
         </is>
       </c>
     </row>
@@ -3795,12 +3795,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>4509</t>
+          <t>4658</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>17646</t>
+          <t>17723</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3810,12 +3810,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3830,12 +3830,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>6286</t>
+          <t>6038</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>20973</t>
+          <t>20466</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3845,12 +3845,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3865,12 +3865,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>12696</t>
+          <t>13177</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>33030</t>
+          <t>32970</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3880,7 +3880,7 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -3908,12 +3908,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>4294</t>
+          <t>4411</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>15994</t>
+          <t>16658</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3923,12 +3923,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3943,12 +3943,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>12616</t>
+          <t>12961</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>29959</t>
+          <t>31212</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3958,12 +3958,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3978,12 +3978,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>19615</t>
+          <t>20135</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>40989</t>
+          <t>41556</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3993,12 +3993,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,98%</t>
         </is>
       </c>
     </row>
@@ -4021,12 +4021,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>8866</t>
+          <t>8714</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>29207</t>
+          <t>27401</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4041,7 +4041,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>8865</t>
+          <t>8464</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>27600</t>
+          <t>27734</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
@@ -4134,12 +4134,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>1173978</t>
+          <t>1175937</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>1267977</t>
+          <t>1269272</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4149,12 +4149,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>54,86%</t>
+          <t>54,95%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>59,26%</t>
+          <t>59,32%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4169,12 +4169,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>1799</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>12333</t>
+          <t>13001</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>1165854</t>
+          <t>1161259</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>1288817</t>
+          <t>1287452</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>27,31%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>30,28%</t>
         </is>
       </c>
     </row>
@@ -4247,12 +4247,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>76496</t>
+          <t>75443</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>112681</t>
+          <t>112186</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4262,12 +4262,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4282,12 +4282,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>477575</t>
+          <t>476672</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>553038</t>
+          <t>553390</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>26,19%</t>
+          <t>26,2%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>561459</t>
+          <t>565015</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>653263</t>
+          <t>654711</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,4%</t>
         </is>
       </c>
     </row>
@@ -4365,7 +4365,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>10276</t>
+          <t>9147</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4380,7 +4380,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4400,7 +4400,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>5838</t>
+          <t>5548</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4415,7 +4415,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4435,7 +4435,7 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>9094</t>
+          <t>11088</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4450,7 +4450,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,26%</t>
         </is>
       </c>
     </row>
@@ -4473,12 +4473,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>66440</t>
+          <t>64618</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>101891</t>
+          <t>99839</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4488,12 +4488,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4508,12 +4508,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>48793</t>
+          <t>49175</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>80321</t>
+          <t>80018</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4523,12 +4523,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4543,12 +4543,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>123011</t>
+          <t>122776</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>169233</t>
+          <t>170559</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4563,7 +4563,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,01%</t>
         </is>
       </c>
     </row>
@@ -4586,12 +4586,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>661222</t>
+          <t>661073</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>751568</t>
+          <t>752638</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4601,12 +4601,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>30,9%</t>
+          <t>30,89%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>35,12%</t>
+          <t>35,17%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4621,12 +4621,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>1454674</t>
+          <t>1452531</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>1536015</t>
+          <t>1536680</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4636,12 +4636,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>68,88%</t>
+          <t>68,78%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>72,73%</t>
+          <t>72,76%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4656,12 +4656,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>2140430</t>
+          <t>2132983</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>2271614</t>
+          <t>2266931</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4671,12 +4671,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>50,34%</t>
+          <t>50,17%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>53,43%</t>
+          <t>53,32%</t>
         </is>
       </c>
     </row>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7699</t>
+          <t>6386</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5102,7 +5102,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5122,7 +5122,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7230</t>
+          <t>7246</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5160,12 +5160,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3092</t>
+          <t>3124</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13840</t>
+          <t>14521</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5180,7 +5180,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5195,12 +5195,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>18980</t>
+          <t>18247</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>41628</t>
+          <t>42241</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5210,12 +5210,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5230,12 +5230,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>25048</t>
+          <t>24522</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>48963</t>
+          <t>49199</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5245,12 +5245,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,18%</t>
         </is>
       </c>
     </row>
@@ -5273,12 +5273,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>995</t>
+          <t>966</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8943</t>
+          <t>8851</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5293,7 +5293,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5313,7 +5313,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11275</t>
+          <t>10943</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5328,7 +5328,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5343,12 +5343,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2807</t>
+          <t>2802</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>13499</t>
+          <t>14424</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5363,7 +5363,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,93%</t>
         </is>
       </c>
     </row>
@@ -5386,12 +5386,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>365863</t>
+          <t>365719</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>416731</t>
+          <t>416013</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5401,12 +5401,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>52,91%</t>
+          <t>52,89%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>60,27%</t>
+          <t>60,16%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5426,7 +5426,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5955</t>
+          <t>5633</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5441,7 +5441,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5456,12 +5456,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>355154</t>
+          <t>358632</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>428766</t>
+          <t>430314</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5471,12 +5471,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>23,16%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>27,79%</t>
         </is>
       </c>
     </row>
@@ -5499,12 +5499,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>68032</t>
+          <t>71283</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>105952</t>
+          <t>106254</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5514,12 +5514,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5534,12 +5534,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>392262</t>
+          <t>391721</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>452781</t>
+          <t>451123</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5549,12 +5549,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>45,77%</t>
+          <t>45,71%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>52,84%</t>
+          <t>52,64%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5569,12 +5569,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>468909</t>
+          <t>471832</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>545652</t>
+          <t>545973</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5584,12 +5584,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>30,28%</t>
+          <t>30,47%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>35,24%</t>
+          <t>35,26%</t>
         </is>
       </c>
     </row>
@@ -5617,7 +5617,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6288</t>
+          <t>7190</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5632,7 +5632,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5652,7 +5652,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6693</t>
+          <t>7369</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5667,7 +5667,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5682,12 +5682,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1038</t>
+          <t>1041</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>10496</t>
+          <t>10588</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>57138</t>
+          <t>58387</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>92821</t>
+          <t>91216</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5760,12 +5760,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>93613</t>
+          <t>92305</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>134090</t>
+          <t>134141</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5775,7 +5775,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -5795,12 +5795,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>157938</t>
+          <t>157773</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>212351</t>
+          <t>213425</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5810,12 +5810,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,78%</t>
         </is>
       </c>
     </row>
@@ -5838,12 +5838,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>105555</t>
+          <t>107203</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>146838</t>
+          <t>147718</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5853,12 +5853,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5873,12 +5873,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>256517</t>
+          <t>258378</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>315555</t>
+          <t>316033</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5888,12 +5888,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>29,93%</t>
+          <t>30,15%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>36,82%</t>
+          <t>36,88%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5908,12 +5908,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>379182</t>
+          <t>378953</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>449910</t>
+          <t>450646</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5923,12 +5923,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>24,47%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>29,06%</t>
+          <t>29,1%</t>
         </is>
       </c>
     </row>
@@ -6068,12 +6068,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>958</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12982</t>
+          <t>13771</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6138,12 +6138,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>952</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>13958</t>
+          <t>12976</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6158,7 +6158,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,55%</t>
         </is>
       </c>
     </row>
@@ -6181,12 +6181,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2835</t>
+          <t>2955</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>15697</t>
+          <t>16965</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6196,12 +6196,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6216,12 +6216,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>16627</t>
+          <t>16814</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>40256</t>
+          <t>39762</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6231,12 +6231,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6251,12 +6251,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>22504</t>
+          <t>22007</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>49477</t>
+          <t>48551</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6266,12 +6266,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,07%</t>
         </is>
       </c>
     </row>
@@ -6294,12 +6294,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3730</t>
+          <t>2918</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>15189</t>
+          <t>13613</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6309,12 +6309,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -6329,12 +6329,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1948</t>
+          <t>1914</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>13669</t>
+          <t>14497</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6349,7 +6349,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -6364,12 +6364,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7583</t>
+          <t>7568</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>23222</t>
+          <t>23702</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -6384,7 +6384,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,01%</t>
         </is>
       </c>
     </row>
@@ -6407,12 +6407,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>468479</t>
+          <t>465640</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>541302</t>
+          <t>540692</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6422,12 +6422,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>38,61%</t>
+          <t>38,38%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>44,62%</t>
+          <t>44,57%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6447,7 +6447,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9806</t>
+          <t>12353</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6462,7 +6462,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6477,12 +6477,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>463393</t>
+          <t>465088</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>546120</t>
+          <t>544494</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>23,17%</t>
         </is>
       </c>
     </row>
@@ -6520,12 +6520,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>17066</t>
+          <t>16034</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>38891</t>
+          <t>38312</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6535,12 +6535,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6555,12 +6555,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>79761</t>
+          <t>81119</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>119310</t>
+          <t>120242</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6570,12 +6570,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6590,12 +6590,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>102963</t>
+          <t>102208</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>149930</t>
+          <t>149213</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,35%</t>
         </is>
       </c>
     </row>
@@ -6633,12 +6633,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1882</t>
+          <t>1885</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>11330</t>
+          <t>10538</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6653,7 +6653,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6673,7 +6673,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5862</t>
+          <t>7080</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6688,42 +6688,42 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
+          <t>0,62%</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>5933</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>2095</t>
+        </is>
+      </c>
+      <c r="T18" s="2" t="inlineStr">
+        <is>
+          <t>12121</t>
+        </is>
+      </c>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>0,25%</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>0,09%</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
           <t>0,52%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>5933</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>1923</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>13085</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>0,25%</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>0,08%</t>
-        </is>
-      </c>
-      <c r="W18" s="2" t="inlineStr">
-        <is>
-          <t>0,56%</t>
         </is>
       </c>
     </row>
@@ -6746,12 +6746,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>154836</t>
+          <t>157646</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>204274</t>
+          <t>206920</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6781,12 +6781,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>161716</t>
+          <t>163235</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>217450</t>
+          <t>213824</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6816,12 +6816,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>331072</t>
+          <t>332660</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>401462</t>
+          <t>405236</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>17,24%</t>
         </is>
       </c>
     </row>
@@ -6859,12 +6859,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>440415</t>
+          <t>446755</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>517676</t>
+          <t>518750</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>36,3%</t>
+          <t>36,82%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>42,67%</t>
+          <t>42,76%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>783331</t>
+          <t>781310</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>848231</t>
+          <t>846581</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>68,88%</t>
+          <t>68,7%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>74,58%</t>
+          <t>74,44%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6929,12 +6929,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1251504</t>
+          <t>1248020</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1351555</t>
+          <t>1346336</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>53,24%</t>
+          <t>53,1%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>57,5%</t>
+          <t>57,28%</t>
         </is>
       </c>
     </row>
@@ -7094,7 +7094,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>10543</t>
+          <t>11121</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7109,7 +7109,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7129,7 +7129,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>7668</t>
+          <t>9075</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7144,7 +7144,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7164,7 +7164,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>14832</t>
+          <t>12970</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7179,7 +7179,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,15%</t>
         </is>
       </c>
     </row>
@@ -7207,7 +7207,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>7535</t>
+          <t>7707</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7222,7 +7222,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7237,12 +7237,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>933</t>
+          <t>978</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>10037</t>
+          <t>10521</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7252,12 +7252,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7272,12 +7272,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2058</t>
+          <t>2064</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>12773</t>
+          <t>13131</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -7292,7 +7292,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,18%</t>
         </is>
       </c>
     </row>
@@ -7315,12 +7315,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4914</t>
+          <t>4477</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>20714</t>
+          <t>20862</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -7355,7 +7355,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>4889</t>
+          <t>5583</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -7370,7 +7370,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -7385,12 +7385,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>5523</t>
+          <t>5215</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>22118</t>
+          <t>22789</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -7400,12 +7400,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,78%</t>
         </is>
       </c>
     </row>
@@ -7428,12 +7428,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>52097</t>
+          <t>54030</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>84049</t>
+          <t>85906</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>27,56%</t>
+          <t>28,17%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7498,12 +7498,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>53567</t>
+          <t>52363</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>86051</t>
+          <t>85106</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7513,12 +7513,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>14,13%</t>
         </is>
       </c>
     </row>
@@ -7541,12 +7541,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>4473</t>
+          <t>5307</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>22434</t>
+          <t>22872</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7556,12 +7556,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7576,12 +7576,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>11618</t>
+          <t>11595</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>31307</t>
+          <t>33097</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7591,12 +7591,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7611,12 +7611,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>19703</t>
+          <t>20803</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>45748</t>
+          <t>45652</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7626,12 +7626,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,58%</t>
         </is>
       </c>
     </row>
@@ -7767,12 +7767,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>18306</t>
+          <t>18745</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>42249</t>
+          <t>42523</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7782,12 +7782,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7802,12 +7802,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>10594</t>
+          <t>10613</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>27606</t>
+          <t>29031</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7817,12 +7817,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7837,12 +7837,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>32261</t>
+          <t>32290</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>62622</t>
+          <t>61023</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7857,7 +7857,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,13%</t>
         </is>
       </c>
     </row>
@@ -7880,12 +7880,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>163628</t>
+          <t>164338</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>201251</t>
+          <t>200636</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7895,12 +7895,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>53,66%</t>
+          <t>53,89%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>66,0%</t>
+          <t>65,79%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7915,12 +7915,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>238896</t>
+          <t>237256</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>264906</t>
+          <t>265153</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7930,12 +7930,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>80,35%</t>
+          <t>79,8%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>89,1%</t>
+          <t>89,18%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7950,12 +7950,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>412539</t>
+          <t>412177</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>459850</t>
+          <t>459444</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7965,12 +7965,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>68,5%</t>
+          <t>68,44%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>76,35%</t>
+          <t>76,29%</t>
         </is>
       </c>
     </row>
@@ -8110,12 +8110,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1863</t>
+          <t>1872</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>16093</t>
+          <t>17388</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8130,7 +8130,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8145,12 +8145,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>996</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>11827</t>
+          <t>11294</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8165,7 +8165,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8180,12 +8180,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>4630</t>
+          <t>4750</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>21657</t>
+          <t>21702</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8195,7 +8195,7 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>9214</t>
+          <t>9199</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>28327</t>
+          <t>27357</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8243,72 +8243,72 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
+          <t>1,24%</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>57892</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>42366</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>75814</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>2,53%</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>1,85%</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>3,31%</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t>74467</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t>57731</t>
+        </is>
+      </c>
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t>95757</t>
+        </is>
+      </c>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>1,65%</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
           <t>1,28%</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>57892</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="inlineStr">
-        <is>
-          <t>43438</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr">
-        <is>
-          <t>78345</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr">
-        <is>
-          <t>2,53%</t>
-        </is>
-      </c>
-      <c r="O32" s="2" t="inlineStr">
-        <is>
-          <t>1,9%</t>
-        </is>
-      </c>
-      <c r="P32" s="2" t="inlineStr">
-        <is>
-          <t>3,42%</t>
-        </is>
-      </c>
-      <c r="Q32" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="R32" s="2" t="inlineStr">
-        <is>
-          <t>74467</t>
-        </is>
-      </c>
-      <c r="S32" s="2" t="inlineStr">
-        <is>
-          <t>57950</t>
-        </is>
-      </c>
-      <c r="T32" s="2" t="inlineStr">
-        <is>
-          <t>95783</t>
-        </is>
-      </c>
-      <c r="U32" s="2" t="inlineStr">
-        <is>
-          <t>1,65%</t>
-        </is>
-      </c>
-      <c r="V32" s="2" t="inlineStr">
-        <is>
-          <t>1,29%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -8336,12 +8336,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>13897</t>
+          <t>13993</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>34861</t>
+          <t>34882</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -8371,12 +8371,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>4777</t>
+          <t>4798</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>19237</t>
+          <t>19455</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -8391,7 +8391,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -8406,12 +8406,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>21700</t>
+          <t>20878</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>45954</t>
+          <t>46587</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,03%</t>
         </is>
       </c>
     </row>
@@ -8449,12 +8449,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>913245</t>
+          <t>913361</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>1009093</t>
+          <t>1008709</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8464,12 +8464,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>41,33%</t>
+          <t>41,34%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>45,67%</t>
+          <t>45,65%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>1039</t>
+          <t>1034</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>13158</t>
+          <t>10907</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8504,7 +8504,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8519,12 +8519,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>911321</t>
+          <t>910266</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>1027111</t>
+          <t>1024069</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>22,75%</t>
         </is>
       </c>
     </row>
@@ -8562,12 +8562,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>102959</t>
+          <t>101882</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>152054</t>
+          <t>148407</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -8577,12 +8577,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -8597,12 +8597,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>495959</t>
+          <t>499637</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>581203</t>
+          <t>584440</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -8612,12 +8612,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>21,8%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>25,5%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -8632,12 +8632,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>615540</t>
+          <t>619550</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>713349</t>
+          <t>718762</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -8647,12 +8647,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>15,97%</t>
         </is>
       </c>
     </row>
@@ -8675,12 +8675,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>2919</t>
+          <t>2934</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>13674</t>
+          <t>13510</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -8695,7 +8695,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -8710,12 +8710,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>992</t>
+          <t>994</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>8851</t>
+          <t>10154</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -8730,7 +8730,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -8745,12 +8745,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>5281</t>
+          <t>5158</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>18290</t>
+          <t>18370</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -8760,7 +8760,7 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -8788,12 +8788,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>250963</t>
+          <t>249711</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>315748</t>
+          <t>313058</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -8803,12 +8803,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -8823,12 +8823,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>285507</t>
+          <t>285858</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>350339</t>
+          <t>356654</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -8838,12 +8838,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -8858,12 +8858,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>551229</t>
+          <t>549999</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>647082</t>
+          <t>643612</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -8873,12 +8873,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,3%</t>
         </is>
       </c>
     </row>
@@ -8901,12 +8901,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>743686</t>
+          <t>742855</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>832856</t>
+          <t>837410</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -8916,12 +8916,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>33,66%</t>
+          <t>33,62%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>37,69%</t>
+          <t>37,9%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -8936,12 +8936,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>1301316</t>
+          <t>1305083</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>1402010</t>
+          <t>1406276</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -8951,12 +8951,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>56,79%</t>
+          <t>56,95%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>61,18%</t>
+          <t>61,37%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -8971,12 +8971,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>2072822</t>
+          <t>2074657</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>2215621</t>
+          <t>2218003</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -8986,12 +8986,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>46,05%</t>
+          <t>46,09%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>49,22%</t>
+          <t>49,28%</t>
         </is>
       </c>
     </row>
@@ -9367,7 +9367,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6759</t>
+          <t>7478</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9382,7 +9382,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9397,12 +9397,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>986</t>
+          <t>974</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9224</t>
+          <t>9891</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9417,7 +9417,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9432,12 +9432,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2045</t>
+          <t>2031</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12263</t>
+          <t>11584</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9447,12 +9447,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,05%</t>
         </is>
       </c>
     </row>
@@ -9475,12 +9475,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2075</t>
+          <t>2098</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12558</t>
+          <t>11747</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9490,12 +9490,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9510,12 +9510,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2271</t>
+          <t>3007</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14364</t>
+          <t>13983</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9525,12 +9525,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9545,12 +9545,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>6428</t>
+          <t>6315</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>21148</t>
+          <t>20955</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9560,12 +9560,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,9%</t>
         </is>
       </c>
     </row>
@@ -9593,7 +9593,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5798</t>
+          <t>6120</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9608,7 +9608,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9663,7 +9663,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>4862</t>
+          <t>5108</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9678,7 +9678,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,46%</t>
         </is>
       </c>
     </row>
@@ -9701,12 +9701,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>278183</t>
+          <t>279253</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>324669</t>
+          <t>322304</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -9716,12 +9716,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>55,14%</t>
+          <t>55,35%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>64,36%</t>
+          <t>63,89%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9741,7 +9741,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6037</t>
+          <t>6888</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9771,12 +9771,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>271937</t>
+          <t>276496</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>331315</t>
+          <t>333957</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9786,12 +9786,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>25,04%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>30,0%</t>
+          <t>30,24%</t>
         </is>
       </c>
     </row>
@@ -9814,12 +9814,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>37385</t>
+          <t>38596</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>64592</t>
+          <t>63999</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9829,12 +9829,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9849,12 +9849,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>333445</t>
+          <t>330257</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>380989</t>
+          <t>380070</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9864,12 +9864,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>55,59%</t>
+          <t>55,05%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>63,51%</t>
+          <t>63,36%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9884,12 +9884,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>373819</t>
+          <t>375270</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>437125</t>
+          <t>442470</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9899,12 +9899,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>33,85%</t>
+          <t>33,98%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>39,58%</t>
+          <t>40,07%</t>
         </is>
       </c>
     </row>
@@ -9932,7 +9932,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5076</t>
+          <t>5473</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9947,7 +9947,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -9967,7 +9967,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7075</t>
+          <t>7023</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9982,7 +9982,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -9997,12 +9997,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>889</t>
+          <t>878</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>7693</t>
+          <t>8673</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10017,7 +10017,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,79%</t>
         </is>
       </c>
     </row>
@@ -10040,12 +10040,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>59123</t>
+          <t>59699</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>91510</t>
+          <t>90472</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10055,12 +10055,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10075,12 +10075,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>74883</t>
+          <t>74920</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>109429</t>
+          <t>109443</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10090,7 +10090,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -10110,12 +10110,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>142768</t>
+          <t>143685</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>190050</t>
+          <t>190589</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10125,12 +10125,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>17,26%</t>
         </is>
       </c>
     </row>
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>54822</t>
+          <t>53371</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>86539</t>
+          <t>85009</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10168,12 +10168,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10188,12 +10188,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>120030</t>
+          <t>119878</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>160573</t>
+          <t>160273</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10203,12 +10203,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>26,72%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10223,12 +10223,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>183265</t>
+          <t>183285</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>234416</t>
+          <t>235163</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10238,12 +10238,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>21,29%</t>
         </is>
       </c>
     </row>
@@ -10388,7 +10388,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6711</t>
+          <t>5838</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10403,77 +10403,77 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
+          <t>0,45%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>4182</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>1115</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>10019</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>0,35%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>0,09%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>0,83%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>6098</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>2720</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>13100</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,24%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>0,11%</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
           <t>0,52%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>4182</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>1117</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>10545</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,35%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,09%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>0,88%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>6098</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>2184</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>12651</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,24%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,09%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>0,51%</t>
         </is>
       </c>
     </row>
@@ -10496,12 +10496,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5285</t>
+          <t>5293</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>22338</t>
+          <t>22880</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10516,7 +10516,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10531,12 +10531,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>9141</t>
+          <t>9378</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>23340</t>
+          <t>24019</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10546,12 +10546,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10566,12 +10566,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>17288</t>
+          <t>16377</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>38680</t>
+          <t>39529</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10581,12 +10581,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,58%</t>
         </is>
       </c>
     </row>
@@ -10609,12 +10609,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4905</t>
+          <t>4860</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>16572</t>
+          <t>17892</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10629,7 +10629,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -10644,12 +10644,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1896</t>
+          <t>1871</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>12538</t>
+          <t>12000</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10664,7 +10664,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -10679,12 +10679,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>8669</t>
+          <t>8301</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>24238</t>
+          <t>25114</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10694,12 +10694,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,01%</t>
         </is>
       </c>
     </row>
@@ -10722,12 +10722,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>549282</t>
+          <t>550563</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>622682</t>
+          <t>622791</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>42,51%</t>
+          <t>42,61%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>48,19%</t>
+          <t>48,2%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10762,7 +10762,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8324</t>
+          <t>7293</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10777,7 +10777,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10792,12 +10792,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>546195</t>
+          <t>546651</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>631756</t>
+          <t>632533</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10807,12 +10807,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>21,89%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>25,33%</t>
         </is>
       </c>
     </row>
@@ -10835,12 +10835,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>19798</t>
+          <t>20584</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>39554</t>
+          <t>41024</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10870,12 +10870,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>161813</t>
+          <t>160885</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>211460</t>
+          <t>218167</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10905,12 +10905,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>188134</t>
+          <t>188989</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>245110</t>
+          <t>248074</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10920,12 +10920,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,94%</t>
         </is>
       </c>
     </row>
@@ -10988,7 +10988,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6836</t>
+          <t>6093</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11003,7 +11003,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11023,7 +11023,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>6390</t>
+          <t>6646</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11038,7 +11038,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,27%</t>
         </is>
       </c>
     </row>
@@ -11061,12 +11061,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>191572</t>
+          <t>191544</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>244651</t>
+          <t>249798</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11076,12 +11076,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11096,12 +11096,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>161837</t>
+          <t>162918</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>212270</t>
+          <t>211415</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11111,12 +11111,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11131,12 +11131,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>367147</t>
+          <t>368725</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>441470</t>
+          <t>444259</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11146,12 +11146,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>17,79%</t>
         </is>
       </c>
     </row>
@@ -11174,12 +11174,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>401527</t>
+          <t>403443</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>471793</t>
+          <t>471303</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11189,12 +11189,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>31,07%</t>
+          <t>31,22%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>36,51%</t>
+          <t>36,47%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11209,12 +11209,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>770481</t>
+          <t>771211</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>832799</t>
+          <t>837279</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>63,95%</t>
+          <t>64,02%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>69,13%</t>
+          <t>69,5%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11244,12 +11244,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1184485</t>
+          <t>1185723</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1286736</t>
+          <t>1286607</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11259,7 +11259,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>47,44%</t>
+          <t>47,49%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -11409,7 +11409,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>9389</t>
+          <t>8087</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11424,7 +11424,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11444,7 +11444,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>6243</t>
+          <t>5927</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11459,7 +11459,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11479,7 +11479,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>10678</t>
+          <t>8583</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11494,7 +11494,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,27%</t>
         </is>
       </c>
     </row>
@@ -11522,7 +11522,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>5551</t>
+          <t>5494</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11537,7 +11537,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11592,7 +11592,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5158</t>
+          <t>5191</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11630,12 +11630,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2260</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>13501</t>
+          <t>13271</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11645,12 +11645,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2756</t>
+          <t>2186</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>13118</t>
+          <t>13415</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -11715,12 +11715,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,99%</t>
         </is>
       </c>
     </row>
@@ -11743,12 +11743,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>72481</t>
+          <t>73602</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>106769</t>
+          <t>108020</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -11758,12 +11758,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>30,82%</t>
+          <t>31,18%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -11813,12 +11813,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>72763</t>
+          <t>73637</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>110961</t>
+          <t>111206</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -11828,12 +11828,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>16,5%</t>
         </is>
       </c>
     </row>
@@ -11856,12 +11856,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>7438</t>
+          <t>7475</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>24334</t>
+          <t>21982</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11871,12 +11871,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11891,12 +11891,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>17317</t>
+          <t>17092</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>38544</t>
+          <t>38802</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11906,12 +11906,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11926,12 +11926,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>28311</t>
+          <t>28747</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>55546</t>
+          <t>55721</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -11941,12 +11941,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,27%</t>
         </is>
       </c>
     </row>
@@ -11974,7 +11974,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>5900</t>
+          <t>5731</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -11989,7 +11989,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -12044,7 +12044,7 @@
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>5938</t>
+          <t>6076</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -12059,7 +12059,7 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,9%</t>
         </is>
       </c>
     </row>
@@ -12082,12 +12082,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>29328</t>
+          <t>30748</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>56339</t>
+          <t>56396</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -12097,12 +12097,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -12117,12 +12117,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>20176</t>
+          <t>20679</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>40745</t>
+          <t>42277</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -12132,12 +12132,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -12152,12 +12152,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>57540</t>
+          <t>57270</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>90366</t>
+          <t>90781</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -12167,12 +12167,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,47%</t>
         </is>
       </c>
     </row>
@@ -12195,12 +12195,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>171166</t>
+          <t>170430</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>210007</t>
+          <t>210210</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -12210,12 +12210,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>49,41%</t>
+          <t>49,2%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>60,63%</t>
+          <t>60,69%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -12230,12 +12230,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>255802</t>
+          <t>254974</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>283233</t>
+          <t>283757</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -12245,12 +12245,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>78,12%</t>
+          <t>77,86%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>86,49%</t>
+          <t>86,65%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -12265,12 +12265,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>433317</t>
+          <t>433963</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>484453</t>
+          <t>485884</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -12280,12 +12280,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>64,3%</t>
+          <t>64,4%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>71,89%</t>
+          <t>72,11%</t>
         </is>
       </c>
     </row>
@@ -12425,12 +12425,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1821</t>
+          <t>1904</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>13378</t>
+          <t>12347</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -12440,12 +12440,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -12460,12 +12460,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>4928</t>
+          <t>4225</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>17407</t>
+          <t>16617</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -12475,12 +12475,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -12495,12 +12495,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>8630</t>
+          <t>8271</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>24248</t>
+          <t>24472</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -12510,7 +12510,7 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -12538,12 +12538,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>10413</t>
+          <t>10505</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>30533</t>
+          <t>28408</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -12558,7 +12558,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -12573,12 +12573,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>13388</t>
+          <t>12641</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>32794</t>
+          <t>31547</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -12588,47 +12588,47 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
+          <t>0,59%</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>1,48%</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t>39630</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t>26916</t>
+        </is>
+      </c>
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t>56030</t>
+        </is>
+      </c>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>0,93%</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
           <t>0,63%</t>
         </is>
       </c>
-      <c r="P32" s="2" t="inlineStr">
-        <is>
-          <t>1,54%</t>
-        </is>
-      </c>
-      <c r="Q32" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="R32" s="2" t="inlineStr">
-        <is>
-          <t>39630</t>
-        </is>
-      </c>
-      <c r="S32" s="2" t="inlineStr">
-        <is>
-          <t>28277</t>
-        </is>
-      </c>
-      <c r="T32" s="2" t="inlineStr">
-        <is>
-          <t>56364</t>
-        </is>
-      </c>
-      <c r="U32" s="2" t="inlineStr">
-        <is>
-          <t>0,93%</t>
-        </is>
-      </c>
-      <c r="V32" s="2" t="inlineStr">
-        <is>
-          <t>0,66%</t>
-        </is>
-      </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,31%</t>
         </is>
       </c>
     </row>
@@ -12651,12 +12651,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>10481</t>
+          <t>10050</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>27266</t>
+          <t>27217</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -12666,7 +12666,7 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
@@ -12686,12 +12686,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>1891</t>
+          <t>1894</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>12959</t>
+          <t>12498</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -12706,7 +12706,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -12721,12 +12721,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>14119</t>
+          <t>13621</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>32826</t>
+          <t>34100</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -12736,12 +12736,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,8%</t>
         </is>
       </c>
     </row>
@@ -12764,12 +12764,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>927709</t>
+          <t>925398</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>1022289</t>
+          <t>1021322</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -12779,12 +12779,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>43,29%</t>
+          <t>43,18%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>47,7%</t>
+          <t>47,66%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -12799,12 +12799,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>1008</t>
+          <t>1003</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>10545</t>
+          <t>9461</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -12819,7 +12819,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -12834,12 +12834,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>925674</t>
+          <t>923740</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>1037282</t>
+          <t>1034075</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12849,12 +12849,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>24,19%</t>
         </is>
       </c>
     </row>
@@ -12877,12 +12877,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>75904</t>
+          <t>75752</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>112850</t>
+          <t>111348</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -12892,12 +12892,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -12912,12 +12912,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>526275</t>
+          <t>525857</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>613606</t>
+          <t>616393</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -12927,12 +12927,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>24,66%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>28,78%</t>
+          <t>28,91%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -12947,12 +12947,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>616834</t>
+          <t>612599</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>712574</t>
+          <t>714003</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -12962,12 +12962,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,7%</t>
         </is>
       </c>
     </row>
@@ -12990,12 +12990,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>885</t>
+          <t>886</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>8326</t>
+          <t>7627</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -13010,7 +13010,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -13025,12 +13025,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>1008</t>
+          <t>1002</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>9434</t>
+          <t>9042</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -13045,7 +13045,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -13060,12 +13060,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>2812</t>
+          <t>2784</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>13255</t>
+          <t>14392</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -13080,7 +13080,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,34%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>302699</t>
+          <t>301948</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>374299</t>
+          <t>369013</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>277838</t>
+          <t>276749</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>341710</t>
+          <t>343337</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>593020</t>
+          <t>594737</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>690614</t>
+          <t>694495</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>16,25%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>651641</t>
+          <t>651858</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>743304</t>
+          <t>741888</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>30,41%</t>
+          <t>30,42%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>34,69%</t>
+          <t>34,62%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>1164156</t>
+          <t>1164068</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>1255122</t>
+          <t>1255810</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -13271,7 +13271,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>58,87%</t>
+          <t>58,9%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1838484</t>
+          <t>1830519</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1974229</t>
+          <t>1971864</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>43,0%</t>
+          <t>42,82%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>46,18%</t>
+          <t>46,12%</t>
         </is>
       </c>
     </row>
